--- a/第6回_Transformer_Block/excel_transformer_block_demo.xlsx
+++ b/第6回_Transformer_Block/excel_transformer_block_demo.xlsx
@@ -100,7 +100,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -122,11 +122,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <right/>
+      <bottom style="thin">
+        <color rgb="00D8DEE9"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -161,6 +167,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -539,7 +548,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>Excelで体験する言語モデルのしくみ 第6回 Transformer Block</t>
         </is>
@@ -652,7 +661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F73"/>
+  <dimension ref="A1:A65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="130" customWidth="1" min="1" max="1"/>
@@ -664,473 +673,422 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>11_PYTHON_CODE: Python in Excelへ貼り付けるコード</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
     </row>
     <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="3" t="n"/>
-    </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>外部 .py ファイルと同じ内容です。Excelの入力表を xl(...) で参照します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1"/>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" t="inlineStr">
         <is>
           <t>import pandas as pd</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" t="inlineStr">
         <is>
           <t>import numpy as np</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="3" t="inlineStr"/>
-    </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>tokens = ["今日", "猫", "ごはん", "食べる"]</t>
-        </is>
-      </c>
+      <c r="A6" t="inlineStr"/>
     </row>
     <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>dims = ["d1:意味", "d2:主語", "d3:動作", "d4:時制"]</t>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>input_source_df = xl("'01_INPUT'!A6:E10", headers=True).dropna(how="all")</t>
         </is>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="3" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>attention_source_df = xl("'01_INPUT'!H6:L10", headers=True).dropna(how="all")</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>X = np.array([</t>
-        </is>
-      </c>
+      <c r="A9" t="inlineStr"/>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    [0.20, 0.10, 0.00, 0.70],</t>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>tokens = input_source_df["token"].astype(str).tolist()</t>
         </is>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    [0.80, 0.90, 0.10, 0.20],</t>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>dims = [c for c in input_source_df.columns if c != "token"]</t>
         </is>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    [0.50, 0.20, 0.60, 0.10],</t>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>X = input_source_df[dims].astype(float).to_numpy()</t>
         </is>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    [0.30, 0.10, 0.90, 0.40],</t>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>attention_output = attention_source_df[dims].astype(float).to_numpy()</t>
         </is>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" t="inlineStr"/>
+    </row>
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>W1 = np.array([</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="24" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    [0.5, -0.2, 0.1, 0.3, 0.2, -0.1],</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    [0.1, 0.4, -0.3, 0.2, 0.1, 0.2],</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    [0.2, 0.1, 0.5, -0.2, 0.3, 0.1],</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    [-0.1, 0.3, 0.2, 0.4, -0.2, 0.2],</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>])</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="3" t="inlineStr"/>
-    </row>
-    <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>attention_output = np.array([</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    [0.05, 0.00, 0.10, 0.20],</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    [0.30, 0.20, 0.05, 0.00],</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    [0.10, 0.05, 0.25, 0.05],</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    [0.20, 0.10, 0.30, 0.10],</t>
-        </is>
-      </c>
-    </row>
     <row r="21" ht="24" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>W2 = np.array([</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="24" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    [0.3, 0.1, -0.2, 0.2],</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    [-0.1, 0.4, 0.1, 0.0],</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="24" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    [0.2, -0.2, 0.3, 0.1],</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    [0.1, 0.2, -0.1, 0.3],</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    [0.0, 0.1, 0.4, -0.2],</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    [0.2, -0.1, 0.1, 0.2],</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="24" customHeight="1">
+      <c r="A28" t="inlineStr">
         <is>
           <t>])</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="24" customHeight="1">
-      <c r="A22" s="3" t="inlineStr"/>
-    </row>
-    <row r="23" ht="24" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>W1 = np.array([</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    [0.5, -0.2, 0.1, 0.3, 0.2, -0.1],</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    [0.1, 0.4, -0.3, 0.2, 0.1, 0.2],</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="24" customHeight="1">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    [0.2, 0.1, 0.5, -0.2, 0.3, 0.1],</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    [-0.1, 0.3, 0.2, 0.4, -0.2, 0.2],</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="24" customHeight="1">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>])</t>
-        </is>
-      </c>
-    </row>
     <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>W2 = np.array([</t>
-        </is>
-      </c>
+      <c r="A29" t="inlineStr"/>
     </row>
     <row r="30" ht="24" customHeight="1">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    [0.3, 0.1, -0.2, 0.2],</t>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>def layer_norm(a, eps=1e-5):</t>
         </is>
       </c>
     </row>
     <row r="31" ht="24" customHeight="1">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    [-0.1, 0.4, 0.1, 0.0],</t>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    mean = a.mean(axis=1, keepdims=True)</t>
         </is>
       </c>
     </row>
     <row r="32" ht="24" customHeight="1">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    [0.2, -0.2, 0.3, 0.1],</t>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    var = ((a - mean) ** 2).mean(axis=1, keepdims=True)</t>
         </is>
       </c>
     </row>
     <row r="33" ht="24" customHeight="1">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    [0.1, 0.2, -0.1, 0.3],</t>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    return (a - mean) / np.sqrt(var + eps)</t>
         </is>
       </c>
     </row>
     <row r="34" ht="24" customHeight="1">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    [0.0, 0.1, 0.4, -0.2],</t>
-        </is>
-      </c>
+      <c r="A34" t="inlineStr"/>
     </row>
     <row r="35" ht="24" customHeight="1">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    [0.2, -0.1, 0.1, 0.2],</t>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>def df(name, arr):</t>
         </is>
       </c>
     </row>
     <row r="36" ht="24" customHeight="1">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>])</t>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    out = pd.DataFrame(np.round(arr, 4), columns=dims)</t>
         </is>
       </c>
     </row>
     <row r="37" ht="24" customHeight="1">
-      <c r="A37" s="3" t="inlineStr"/>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    out.insert(0, "token", tokens)</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="24" customHeight="1">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>def layer_norm(a, eps=1e-5):</t>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    out.insert(1, "stage", name)</t>
         </is>
       </c>
     </row>
     <row r="39" ht="24" customHeight="1">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    mean = a.mean(axis=1, keepdims=True)</t>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    return out</t>
         </is>
       </c>
     </row>
     <row r="40" ht="24" customHeight="1">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    var = ((a - mean) ** 2).mean(axis=1, keepdims=True)</t>
-        </is>
-      </c>
+      <c r="A40" t="inlineStr"/>
     </row>
     <row r="41" ht="24" customHeight="1">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    return (a - mean) / np.sqrt(var + eps)</t>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>add1 = X + attention_output</t>
         </is>
       </c>
     </row>
     <row r="42" ht="24" customHeight="1">
-      <c r="A42" s="3" t="inlineStr"/>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>norm1 = layer_norm(add1)</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="24" customHeight="1">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>def df(name, arr):</t>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>ffn_hidden = np.maximum(0, norm1 @ W1)</t>
         </is>
       </c>
     </row>
     <row r="44" ht="24" customHeight="1">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    out = pd.DataFrame(np.round(arr, 4), columns=dims)</t>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>ffn_output = ffn_hidden @ W2</t>
         </is>
       </c>
     </row>
     <row r="45" ht="24" customHeight="1">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    out.insert(0, "token", tokens)</t>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>add2 = norm1 + ffn_output</t>
         </is>
       </c>
     </row>
     <row r="46" ht="24" customHeight="1">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    out.insert(1, "stage", name)</t>
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>block_output = layer_norm(add2)</t>
         </is>
       </c>
     </row>
     <row r="47" ht="24" customHeight="1">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    return out</t>
-        </is>
-      </c>
+      <c r="A47" t="inlineStr"/>
     </row>
     <row r="48" ht="24" customHeight="1">
-      <c r="A48" s="3" t="inlineStr"/>
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>flow_df = pd.concat([</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="24" customHeight="1">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>add1 = X + attention_output</t>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    df("Input X", X),</t>
         </is>
       </c>
     </row>
     <row r="50" ht="24" customHeight="1">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t>norm1 = layer_norm(add1)</t>
+      <c r="A50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    df("Attention Output", attention_output),</t>
         </is>
       </c>
     </row>
     <row r="51" ht="24" customHeight="1">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>ffn_hidden = np.maximum(0, norm1 @ W1)</t>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    df("Add1 = X + Attention", add1),</t>
         </is>
       </c>
     </row>
     <row r="52" ht="24" customHeight="1">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>ffn_output = ffn_hidden @ W2</t>
+      <c r="A52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    df("Norm1 = LayerNorm(Add1)", norm1),</t>
         </is>
       </c>
     </row>
     <row r="53" ht="24" customHeight="1">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>add2 = norm1 + ffn_output</t>
+      <c r="A53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    df("FFN Output", ffn_output),</t>
         </is>
       </c>
     </row>
     <row r="54" ht="24" customHeight="1">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>block_output = layer_norm(add2)</t>
+      <c r="A54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    df("Add2 = Norm1 + FFN", add2),</t>
         </is>
       </c>
     </row>
     <row r="55" ht="24" customHeight="1">
-      <c r="A55" s="3" t="inlineStr"/>
+      <c r="A55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    df("Block Output", block_output),</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="24" customHeight="1">
-      <c r="A56" s="3" t="inlineStr">
-        <is>
-          <t>flow_df = pd.concat([</t>
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>], ignore_index=True)</t>
         </is>
       </c>
     </row>
     <row r="57" ht="24" customHeight="1">
-      <c r="A57" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    df("Input X", X),</t>
-        </is>
-      </c>
+      <c r="A57" t="inlineStr"/>
     </row>
     <row r="58" ht="24" customHeight="1">
-      <c r="A58" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    df("Attention Output", attention_output),</t>
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>trace_df = flow_df[flow_df["token"].eq("食べる")].reset_index(drop=True)</t>
         </is>
       </c>
     </row>
     <row r="59" ht="24" customHeight="1">
-      <c r="A59" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    df("Add1 = X + Attention", add1),</t>
-        </is>
-      </c>
+      <c r="A59" t="inlineStr"/>
     </row>
     <row r="60" ht="24" customHeight="1">
-      <c r="A60" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    df("Norm1 = LayerNorm(Add1)", norm1),</t>
+      <c r="A60" t="inlineStr">
+        <is>
+          <t># Python in Excelで最後に表示したい表を選びます。</t>
         </is>
       </c>
     </row>
     <row r="61" ht="24" customHeight="1">
-      <c r="A61" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    df("FFN Output", ffn_output),</t>
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>result_df = flow_df</t>
         </is>
       </c>
     </row>
     <row r="62" ht="24" customHeight="1">
-      <c r="A62" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    df("Add2 = Norm1 + FFN", add2),</t>
+      <c r="A62" t="inlineStr">
+        <is>
+          <t># result_df = trace_df</t>
         </is>
       </c>
     </row>
     <row r="63" ht="24" customHeight="1">
-      <c r="A63" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    df("Block Output", block_output),</t>
+      <c r="A63" t="inlineStr">
+        <is>
+          <t># result_df = df("Block Output", block_output)</t>
         </is>
       </c>
     </row>
     <row r="64" ht="24" customHeight="1">
-      <c r="A64" s="3" t="inlineStr">
-        <is>
-          <t>], ignore_index=True)</t>
-        </is>
-      </c>
+      <c r="A64" t="inlineStr"/>
     </row>
     <row r="65" ht="24" customHeight="1">
-      <c r="A65" s="3" t="inlineStr"/>
-    </row>
-    <row r="66" ht="24" customHeight="1">
-      <c r="A66" s="3" t="inlineStr">
-        <is>
-          <t>trace_df = flow_df[flow_df["token"].eq("食べる")].reset_index(drop=True)</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="24" customHeight="1">
-      <c r="A67" s="3" t="inlineStr"/>
-    </row>
-    <row r="68" ht="24" customHeight="1">
-      <c r="A68" s="3" t="inlineStr">
-        <is>
-          <t># Python in Excelで最後に表示したい表を選びます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="24" customHeight="1">
-      <c r="A69" s="3" t="inlineStr">
-        <is>
-          <t>result_df = flow_df</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="24" customHeight="1">
-      <c r="A70" s="3" t="inlineStr">
-        <is>
-          <t># result_df = trace_df</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="24" customHeight="1">
-      <c r="A71" s="3" t="inlineStr">
-        <is>
-          <t># result_df = df("Block Output", block_output)</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="24" customHeight="1">
-      <c r="A72" s="3" t="inlineStr"/>
-    </row>
-    <row r="73" ht="24" customHeight="1">
-      <c r="A73" s="3" t="inlineStr">
+      <c r="A65" t="inlineStr">
         <is>
           <t>result_df</t>
         </is>
       </c>
     </row>
+    <row r="66" ht="24" customHeight="1"/>
+    <row r="67" ht="24" customHeight="1"/>
+    <row r="68" ht="24" customHeight="1"/>
+    <row r="69" ht="24" customHeight="1"/>
+    <row r="70" ht="24" customHeight="1"/>
+    <row r="71" ht="24" customHeight="1"/>
+    <row r="72" ht="24" customHeight="1"/>
+    <row r="73" ht="24" customHeight="1"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
@@ -1157,7 +1115,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>12_TROUBLE: よくある確認点</t>
         </is>
@@ -1182,7 +1140,7 @@
           <t>よくある確認点</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n"/>
+      <c r="B4" s="2" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -1271,7 +1229,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>13_SERIES_ROADMAP</t>
         </is>
@@ -1298,8 +1256,8 @@
           <t>全10回ロードマップ</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="3" t="n"/>
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -1521,7 +1479,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>01_INPUT: tokenごとの入力と第5回相当のAttention Output</t>
         </is>
@@ -1558,17 +1516,17 @@
           <t>このシートでは値を確認します。Python in Excelで計算すると、以降のシートと同じ表を再計算できます。</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="3" t="n"/>
-      <c r="G3" s="3" t="n"/>
-      <c r="H3" s="3" t="n"/>
-      <c r="I3" s="3" t="n"/>
-      <c r="J3" s="3" t="n"/>
-      <c r="K3" s="3" t="n"/>
-      <c r="L3" s="3" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
     </row>
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="3" t="n"/>
@@ -1590,10 +1548,10 @@
           <t>Input X</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="n"/>
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="n"/>
       <c r="F5" s="3" t="n"/>
       <c r="G5" s="3" t="n"/>
       <c r="H5" s="4" t="inlineStr">
@@ -1601,10 +1559,10 @@
           <t>Attention Output</t>
         </is>
       </c>
-      <c r="I5" s="3" t="n"/>
-      <c r="J5" s="3" t="n"/>
-      <c r="K5" s="3" t="n"/>
-      <c r="L5" s="3" t="n"/>
+      <c r="I5" s="2" t="n"/>
+      <c r="J5" s="2" t="n"/>
+      <c r="K5" s="2" t="n"/>
+      <c r="L5" s="2" t="n"/>
     </row>
     <row r="6" ht="24" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
@@ -1841,7 +1799,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>02_BLOCK_FLOW: Transformer Blockの処理順</t>
         </is>
@@ -1866,11 +1824,11 @@
           <t>今回の教材では、分かりやすさを優先して Attention Output -&gt; Add &amp; Norm -&gt; FFN -&gt; Add &amp; Norm -&gt; Block Output の順に固定します。</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="3" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
     </row>
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="3" t="n"/>
@@ -1886,8 +1844,8 @@
           <t>処理の流れ</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="3" t="n"/>
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
       <c r="D5" s="3" t="n"/>
       <c r="E5" s="3" t="n"/>
       <c r="F5" s="3" t="n"/>
@@ -2085,7 +2043,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>03_ATTENTION_OUTPUT: Attention Output</t>
         </is>
@@ -2116,10 +2074,10 @@
           <t>Attention Output</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="3" t="n"/>
-      <c r="D4" s="3" t="n"/>
-      <c r="E4" s="3" t="n"/>
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -2257,7 +2215,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>04_ADD_NORM_1: Norm1 = LayerNorm(Add1)</t>
         </is>
@@ -2308,10 +2266,10 @@
           <t>Norm1 = LayerNorm(Add1)</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="3" t="n"/>
-      <c r="D4" s="3" t="n"/>
-      <c r="E4" s="3" t="n"/>
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
       <c r="F4" s="3" t="n"/>
       <c r="G4" s="3" t="n"/>
       <c r="H4" s="4" t="inlineStr">
@@ -2319,10 +2277,10 @@
           <t>Add1 = X + Attention</t>
         </is>
       </c>
-      <c r="I4" s="3" t="n"/>
-      <c r="J4" s="3" t="n"/>
-      <c r="K4" s="3" t="n"/>
-      <c r="L4" s="3" t="n"/>
+      <c r="I4" s="2" t="n"/>
+      <c r="J4" s="2" t="n"/>
+      <c r="K4" s="2" t="n"/>
+      <c r="L4" s="2" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -2563,7 +2521,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>05_FFN: FFN Output</t>
         </is>
@@ -2594,10 +2552,10 @@
           <t>FFN Output</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="3" t="n"/>
-      <c r="D4" s="3" t="n"/>
-      <c r="E4" s="3" t="n"/>
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -2735,7 +2693,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>06_ADD_NORM_2: Block Output = LayerNorm(Add2)</t>
         </is>
@@ -2786,10 +2744,10 @@
           <t>Block Output = LayerNorm(Add2)</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="3" t="n"/>
-      <c r="D4" s="3" t="n"/>
-      <c r="E4" s="3" t="n"/>
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
       <c r="F4" s="3" t="n"/>
       <c r="G4" s="3" t="n"/>
       <c r="H4" s="4" t="inlineStr">
@@ -2797,10 +2755,10 @@
           <t>Add2 = Norm1 + FFN</t>
         </is>
       </c>
-      <c r="I4" s="3" t="n"/>
-      <c r="J4" s="3" t="n"/>
-      <c r="K4" s="3" t="n"/>
-      <c r="L4" s="3" t="n"/>
+      <c r="I4" s="2" t="n"/>
+      <c r="J4" s="2" t="n"/>
+      <c r="K4" s="2" t="n"/>
+      <c r="L4" s="2" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -3041,7 +2999,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>07_BLOCK_OUTPUT: Block Output = LayerNorm(Add2)</t>
         </is>
@@ -3072,10 +3030,10 @@
           <t>Block Output = LayerNorm(Add2)</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="3" t="n"/>
-      <c r="D4" s="3" t="n"/>
-      <c r="E4" s="3" t="n"/>
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -3207,7 +3165,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>10_RUN_PYTHON: Python in Excel 実行手順</t>
         </is>
@@ -3232,7 +3190,7 @@
           <t>実行手順</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n"/>
+      <c r="B4" s="2" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="4" t="inlineStr">

--- a/第6回_Transformer_Block/excel_transformer_block_demo.xlsx
+++ b/第6回_Transformer_Block/excel_transformer_block_demo.xlsx
@@ -132,7 +132,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -170,6 +170,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -661,7 +667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A65"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="130" customWidth="1" min="1" max="1"/>
@@ -701,9 +707,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="24" customHeight="1">
-      <c r="A6" t="inlineStr"/>
-    </row>
+    <row r="6" ht="24" customHeight="1"/>
     <row r="7" ht="24" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
@@ -718,9 +722,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="24" customHeight="1">
-      <c r="A9" t="inlineStr"/>
-    </row>
+    <row r="9" ht="24" customHeight="1"/>
     <row r="10" ht="24" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
@@ -749,9 +751,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="24" customHeight="1">
-      <c r="A14" t="inlineStr"/>
-    </row>
+    <row r="14" ht="24" customHeight="1"/>
     <row r="15" ht="24" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
@@ -850,9 +850,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="24" customHeight="1">
-      <c r="A29" t="inlineStr"/>
-    </row>
+    <row r="29" ht="24" customHeight="1"/>
     <row r="30" ht="24" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
@@ -881,9 +879,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="24" customHeight="1">
-      <c r="A34" t="inlineStr"/>
-    </row>
+    <row r="34" ht="24" customHeight="1"/>
     <row r="35" ht="24" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
@@ -919,9 +915,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="24" customHeight="1">
-      <c r="A40" t="inlineStr"/>
-    </row>
+    <row r="40" ht="24" customHeight="1"/>
     <row r="41" ht="24" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
@@ -964,9 +958,7 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="24" customHeight="1">
-      <c r="A47" t="inlineStr"/>
-    </row>
+    <row r="47" ht="24" customHeight="1"/>
     <row r="48" ht="24" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
@@ -1030,9 +1022,7 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="24" customHeight="1">
-      <c r="A57" t="inlineStr"/>
-    </row>
+    <row r="57" ht="24" customHeight="1"/>
     <row r="58" ht="24" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
@@ -1040,9 +1030,7 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="24" customHeight="1">
-      <c r="A59" t="inlineStr"/>
-    </row>
+    <row r="59" ht="24" customHeight="1"/>
     <row r="60" ht="24" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
@@ -1071,9 +1059,7 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="24" customHeight="1">
-      <c r="A64" t="inlineStr"/>
-    </row>
+    <row r="64" ht="24" customHeight="1"/>
     <row r="65" ht="24" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
@@ -1135,7 +1121,7 @@
       <c r="B3" s="3" t="n"/>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>よくある確認点</t>
         </is>
@@ -1251,7 +1237,7 @@
       <c r="C3" s="3" t="n"/>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>全10回ロードマップ</t>
         </is>
@@ -1511,7 +1497,7 @@
       <c r="L2" s="3" t="n"/>
     </row>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>このシートでは値を確認します。Python in Excelで計算すると、以降のシートと同じ表を再計算できます。</t>
         </is>
@@ -1543,7 +1529,7 @@
       <c r="L4" s="3" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>Input X</t>
         </is>
@@ -1554,7 +1540,7 @@
       <c r="E5" s="2" t="n"/>
       <c r="F5" s="3" t="n"/>
       <c r="G5" s="3" t="n"/>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H5" s="15" t="inlineStr">
         <is>
           <t>Attention Output</t>
         </is>
@@ -1819,7 +1805,7 @@
       <c r="F2" s="3" t="n"/>
     </row>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>今回の教材では、分かりやすさを優先して Attention Output -&gt; Add &amp; Norm -&gt; FFN -&gt; Add &amp; Norm -&gt; Block Output の順に固定します。</t>
         </is>
@@ -1839,7 +1825,7 @@
       <c r="F4" s="3" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>処理の流れ</t>
         </is>
@@ -2069,7 +2055,7 @@
       <c r="E3" s="3" t="n"/>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>Attention Output</t>
         </is>
@@ -2261,7 +2247,7 @@
       <c r="L3" s="3" t="n"/>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>Norm1 = LayerNorm(Add1)</t>
         </is>
@@ -2272,7 +2258,7 @@
       <c r="E4" s="2" t="n"/>
       <c r="F4" s="3" t="n"/>
       <c r="G4" s="3" t="n"/>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H4" s="15" t="inlineStr">
         <is>
           <t>Add1 = X + Attention</t>
         </is>
@@ -2547,7 +2533,7 @@
       <c r="E3" s="3" t="n"/>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>FFN Output</t>
         </is>
@@ -2739,7 +2725,7 @@
       <c r="L3" s="3" t="n"/>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>Block Output = LayerNorm(Add2)</t>
         </is>
@@ -2750,7 +2736,7 @@
       <c r="E4" s="2" t="n"/>
       <c r="F4" s="3" t="n"/>
       <c r="G4" s="3" t="n"/>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H4" s="15" t="inlineStr">
         <is>
           <t>Add2 = Norm1 + FFN</t>
         </is>
@@ -3025,7 +3011,7 @@
       <c r="E3" s="3" t="n"/>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>Block Output = LayerNorm(Add2)</t>
         </is>
@@ -3185,7 +3171,7 @@
       <c r="B3" s="3" t="n"/>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>実行手順</t>
         </is>
